--- a/Enade_2015_Ifes.xlsx
+++ b/Enade_2015_Ifes.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,11 @@
           <t>Situação</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CAMPUS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -528,6 +533,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Barra de São Francisco</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -583,6 +593,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -638,6 +653,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Guarapari</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -693,6 +713,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Linhares</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -748,6 +773,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Santa Maria de Jetibá</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -803,6 +833,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Venda Nova do Imigrante</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -858,6 +893,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -913,6 +953,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -968,6 +1013,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1023,6 +1073,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1078,6 +1133,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1133,6 +1193,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1188,6 +1253,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1243,6 +1313,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1298,6 +1373,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1353,6 +1433,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1408,6 +1493,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1463,6 +1553,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1518,6 +1613,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Venda Nova do Imigrante</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1573,6 +1673,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1628,6 +1733,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1683,6 +1793,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1738,6 +1853,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1793,6 +1913,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Guarapari</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1848,6 +1973,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1903,6 +2033,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ibatiba</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1958,6 +2093,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Nova Venécia</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2013,6 +2153,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2068,6 +2213,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Alegre</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2123,6 +2273,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Linhares</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2178,6 +2333,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2233,6 +2393,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2288,6 +2453,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Piúma</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2343,6 +2513,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2398,6 +2573,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Guarapari</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2453,6 +2633,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>São Mateus</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2508,6 +2693,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2563,6 +2753,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Aracruz</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2618,6 +2813,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2673,6 +2873,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>São Mateus</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2728,6 +2933,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2783,6 +2993,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2838,6 +3053,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2893,6 +3113,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2948,6 +3173,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3003,6 +3233,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3058,6 +3293,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Nova Venécia</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3113,6 +3353,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Nova Venécia</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3168,6 +3413,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Montanha</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3223,6 +3473,11 @@
           <t>Em extinção</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3278,6 +3533,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3333,6 +3593,11 @@
           <t>Em extinção</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3388,6 +3653,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3443,6 +3713,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Venda Nova do Imigrante</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3498,6 +3773,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3553,6 +3833,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3608,6 +3893,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Viana</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3663,6 +3953,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3718,6 +4013,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3773,6 +4073,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3828,6 +4133,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3883,6 +4193,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3938,6 +4253,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3993,6 +4313,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Ibatiba</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4048,6 +4373,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4103,6 +4433,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4158,6 +4493,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4205,6 +4545,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Aracruz</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4252,6 +4597,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4307,6 +4657,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4362,6 +4717,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Aracruz</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4417,6 +4777,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Vila Velha</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4472,6 +4837,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4527,6 +4897,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4582,6 +4957,11 @@
           <t>Em extinção</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4637,6 +5017,11 @@
           <t>Extinto</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4692,6 +5077,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Cachoeiro de Itapemirim</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4747,6 +5137,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Colatina</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4802,6 +5197,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Serra</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4857,6 +5257,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Vários municípios</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4912,6 +5317,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4965,6 +5375,11 @@
       <c r="K83" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Colatina</t>
         </is>
       </c>
     </row>

--- a/Enade_2015_Ifes.xlsx
+++ b/Enade_2015_Ifes.xlsx
@@ -5394,7 +5394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5413,14 +5413,26 @@
           <t>Ano</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Inscritos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Participantes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1457344</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO</t>
+          <t>Sem dados</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5428,1220 +5440,11 @@
           <t>2015</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1319231</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1264959</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1595560</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1458011</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1376048</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1574036</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AGRONOMIA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1117583</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AGRONOMIA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1103831</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AGRONOMIA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>100666</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1666010</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>150129</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1103832</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>66691</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ANÁLISE E DESENVOLVIMENTO DE SISTEMAS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>89040</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AQUICULTURA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1181819</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ARQUITETURA E URBANISMO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1457328</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BIOMEDICINA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1103907</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CAFEICULTURA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1319232</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CIÊNCIA E TECNOLOGIA DE ALIMENTOS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1117313</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS AGRÍCOLAS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1103909</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS BIOLÓGICAS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1288837</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS BIOLÓGICAS</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1103692</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS BIOLÓGICAS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1550806</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS DA NATUREZA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1637375</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CIÊNCIAS ECONÔMICAS</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1382551</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ENGENHARIA AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1457329</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ENGENHARIA CIVIL</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1515614</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ENGENHARIA CIVIL</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1188402</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE AQUICULTURA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1349075</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE CONTROLE E AUTOMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>102499</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE CONTROLE E AUTOMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>123260</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE MINAS</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1181820</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE PESCA</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>121880</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ENGENHARIA DE PRODUÇÃO</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1374889</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ENGENHARIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1477535</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ENGENHARIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>88399</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ENGENHARIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1319229</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1181815</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>123569</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1341020</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ENGENHARIA MECÂNICA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>88396</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ENGENHARIA METALÚRGICA</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1660412</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ENGENHARIA QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>121884</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ENGENHARIA SANITÁRIA E AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1127924</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FÍSICA</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>1288840</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>FÍSICA</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1308687</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>GEOGRAFIA</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>1421000</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>GEOLOGIA</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>1443426</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>GESTÃO AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>123336</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>INFORMÁTICA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>1704263</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>INFORMÁTICA</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>1179970</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>1704262</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1365444</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>1127926</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>50017213</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LETRAS - LÍNGUA PORTUGUESA</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>1330110</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>LOGÍSTICA</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>66694</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>1103657</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MATEMÁTICA</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>108730</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>MATEMÁTICA</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>1691158</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>MEDICINA VETERINÁRIA</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>1693947</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>MEDICINA VETERINÁRIA</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>1319230</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>PEDAGOGIA</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>1617650</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>PEDAGOGIA</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>1457327</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>PEDAGOGIA</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>48223</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>PROCESSOS METALÚRGICOS</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>88403</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>PROCESSOS METALÚRGICOS</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>1117076</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>1127927</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>88401</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>QUÍMICA</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1349076</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>QUÍMICA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1342675</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>QUÍMICA INDUSTRIAL</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>66681</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>REDES DE COMPUTADORES</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>83953</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>REDES DE COMPUTADORES</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>102494</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>SANEAMENTO AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>48225</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>SANEAMENTO AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>1270538</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>SISTEMAS DE INFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>1127925</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>SISTEMAS DE INFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>122845</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>SISTEMAS DE INFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>1607113</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SISTEMAS PARA INTERNET</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>1595496</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>SISTEMAS PARA INTERNET</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>1488260</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>ZOOTECNIA</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
